--- a/trades/by_strategy/live_trendline_reversal.xlsx
+++ b/trades/by_strategy/live_trendline_reversal.xlsx
@@ -535,7 +535,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
@@ -867,28 +867,28 @@
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>224.12</v>
+        <v>176.29</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>253.31</v>
+        <v>201.28</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>14568</v>
+        <v>45835</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>16465</v>
+        <v>52333</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>1820</v>
+        <v>6356</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="10" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -969,28 +969,28 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>208.75</v>
+        <v>164.2</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>208.59</v>
+        <v>164.05</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>27138</v>
+        <v>42692</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>27117</v>
+        <v>42653</v>
       </c>
       <c r="V4" s="17" t="n">
-        <v>-118</v>
+        <v>-166</v>
       </c>
       <c r="W4" s="18" t="n">
         <v>-0.4</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
@@ -1071,28 +1071,28 @@
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>74.59999999999999</v>
+        <v>37.68</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>74.09</v>
+        <v>37.25</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>4849</v>
+        <v>7348</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>4816</v>
+        <v>7264</v>
       </c>
       <c r="V5" s="20" t="n">
-        <v>-89</v>
+        <v>-145</v>
       </c>
       <c r="W5" s="21" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23100 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>120.83</v>
+        <v>76.78</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>99.56</v>
+        <v>61.28</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>7854</v>
+        <v>9981</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>6471</v>
+        <v>7966</v>
       </c>
       <c r="V6" s="17" t="n">
-        <v>-1442</v>
+        <v>-2078</v>
       </c>
       <c r="W6" s="18" t="n">
-        <v>-18.4</v>
+        <v>-20.8</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23000 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
@@ -1275,22 +1275,22 @@
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>130.47</v>
+        <v>89.03</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>159.04</v>
+        <v>111.19</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>16961</v>
+        <v>11574</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>20675</v>
+        <v>14455</v>
       </c>
       <c r="V7" s="14" t="n">
-        <v>3630</v>
+        <v>2808</v>
       </c>
       <c r="W7" s="15" t="n">
-        <v>21.4</v>
+        <v>24.3</v>
       </c>
       <c r="X7" s="9" t="n">
         <v>2</v>

--- a/trades/by_strategy/live_trendline_reversal.xlsx
+++ b/trades/by_strategy/live_trendline_reversal.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -765,22 +765,22 @@
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>2</v>

--- a/trades/by_strategy/live_trendline_reversal.xlsx
+++ b/trades/by_strategy/live_trendline_reversal.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trendline Reversal (Live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trendline Reversal (Live)'!$A$1:$Z$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trendline Reversal (Live)'!$A$1:$Z$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,37 +131,37 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -529,13 +529,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -544,7 +544,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -695,12 +695,12 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -720,89 +720,89 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+1.87R)</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>22610.25</v>
+        <v>22975.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>22575.35</v>
+        <v>22941.5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>22686.15</v>
+        <v>23075.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>34.9</v>
+        <v>33.6</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>22686.15</v>
+        <v>23033.5</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Partial + Structure Trail</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>151.21</v>
+        <v>89.03</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>185.32</v>
+        <v>111.19</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>19657</v>
+        <v>17361</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>24092</v>
+        <v>21682</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>4344</v>
+        <v>4236</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
+          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -822,89 +822,89 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.05R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G3" s="11" t="n">
-        <v>22736.1</v>
+        <v>23096.8</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>22790.35</v>
+        <v>23141.15</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>22491.97</v>
+        <v>22917.3</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>54.25</v>
+        <v>44.35</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>22678.95</v>
+        <v>23141.15</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N3" s="11" t="n">
-        <v>57.15</v>
+        <v>-44.35</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>1.05</v>
+        <v>-1</v>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>176.29</v>
+        <v>76.78</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>201.28</v>
+        <v>61.28</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>45835</v>
+        <v>14972</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>52333</v>
+        <v>11950</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>6356</v>
+        <v>-3093</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>13.9</v>
+        <v>-20.7</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z3" s="10" t="inlineStr">
         <is>
-          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
+          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -928,23 +928,23 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>22781.5</v>
+        <v>22573.4</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>22744.75</v>
+        <v>22617.45</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22891.75</v>
+        <v>22390.45</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>36.75</v>
+        <v>44.05</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>22781.5</v>
+        <v>22573.4</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -956,57 +956,57 @@
         <v>0</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22900 CE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>164.2</v>
+        <v>37.68</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>164.05</v>
+        <v>37.25</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>42692</v>
+        <v>7348</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>42653</v>
+        <v>7264</v>
       </c>
       <c r="V4" s="17" t="n">
-        <v>-166</v>
+        <v>-145</v>
       </c>
       <c r="W4" s="18" t="n">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -1030,23 +1030,23 @@
         </is>
       </c>
       <c r="G5" s="11" t="n">
-        <v>22573.4</v>
+        <v>22781.5</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>22617.45</v>
+        <v>22744.75</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>22390.45</v>
+        <v>22891.75</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>44.05</v>
+        <v>36.75</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>22573.4</v>
+        <v>22781.5</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1058,57 +1058,57 @@
         <v>0</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>37.68</v>
+        <v>164.2</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>37.25</v>
+        <v>164.05</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>7348</v>
+        <v>42692</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>7264</v>
-      </c>
-      <c r="V5" s="20" t="n">
-        <v>-145</v>
-      </c>
-      <c r="W5" s="21" t="n">
-        <v>-2</v>
+        <v>42653</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>-166</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>-0.4</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
-          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1128,89 +1128,89 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+1.05R)</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>23096.8</v>
+        <v>22736.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23141.15</v>
+        <v>22790.35</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22917.3</v>
+        <v>22491.97</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>44.35</v>
+        <v>54.25</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>23141.15</v>
+        <v>22678.95</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <v>-1</v>
+        <v>57.15</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>1.05</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23000 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>76.78</v>
+        <v>176.29</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>61.28</v>
+        <v>201.28</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>9981</v>
+        <v>45835</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>7966</v>
-      </c>
-      <c r="V6" s="17" t="n">
-        <v>-2078</v>
-      </c>
-      <c r="W6" s="18" t="n">
-        <v>-20.8</v>
+        <v>52333</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>6356</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1230,82 +1230,184 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.87R)</t>
+          <t>TRAILED (+0.16R)</t>
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>22975.1</v>
+        <v>22610.25</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>22941.5</v>
+        <v>22575.35</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>23075.9</v>
+        <v>22686.15</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>33.6</v>
+        <v>34.9</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>23033.5</v>
+        <v>22615.85</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Partial + Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N7" s="11" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>1.87</v>
+        <v>5.6</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>0.16</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>89.03</v>
+        <v>151.21</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>111.19</v>
+        <v>153.26</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>11574</v>
+        <v>29486</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>14455</v>
-      </c>
-      <c r="V7" s="14" t="n">
-        <v>2808</v>
-      </c>
-      <c r="W7" s="15" t="n">
-        <v>24.3</v>
+        <v>29886</v>
+      </c>
+      <c r="V7" s="21" t="n">
+        <v>297</v>
+      </c>
+      <c r="W7" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="X7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z7" s="10" t="inlineStr">
         <is>
-          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Micro Trendline Breakdown [1M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TRAILED (+1.00R)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>22852.55</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>22873</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>22780.85</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>22828</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Trailed Stop Hit (+1.0R Locked)</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 22750 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>110.02</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>26616</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>28605</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>10:36 1M CHoCH breakdown of ascending trendline below VWAP. Trailed stop hit at 11:14 IST after +2R milestone reached.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z7"/>
+  <autoFilter ref="A1:Z8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>